--- a/asx_eod_output/Report_XLSX/Report_20260819.xlsx
+++ b/asx_eod_output/Report_XLSX/Report_20260819.xlsx
@@ -515,24 +515,24 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>2.375</v>
+        <v>2.38</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.025</v>
+        <v>0.03</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>1.28%</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
         <v>70000</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>166250</v>
+        <v>166600</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>1750</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="6">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>63.585</v>
+        <v>63.58</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>-0.265</v>
+        <v>-0.27</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -583,10 +583,10 @@
         <v>11065</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>703568.03</v>
+        <v>703512.7</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-2932.23</v>
+        <v>-2987.55</v>
       </c>
     </row>
     <row r="8">
@@ -623,10 +623,10 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>160.18</v>
+        <v>160.17</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>-2.45</v>
+        <v>-2.46</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -677,24 +677,24 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>165.93</v>
+        <v>165.8</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>8.109999999999999</v>
+        <v>7.98</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5.14%</t>
+          <t>5.06%</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
         <v>4000</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>663720</v>
+        <v>663200</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>32440</v>
+        <v>31920</v>
       </c>
     </row>
     <row r="12">
@@ -839,24 +839,24 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>33.605</v>
+        <v>33.6</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>0.445</v>
+        <v>0.44</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>1.33%</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
         <v>1288</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>43283.24</v>
+        <v>43276.8</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>573.16</v>
+        <v>566.72</v>
       </c>
     </row>
     <row r="18">
@@ -870,10 +870,10 @@
       <c r="D18" s="5" t="inlineStr"/>
       <c r="E18" s="7" t="inlineStr"/>
       <c r="F18" s="8" t="n">
-        <v>1904768.89</v>
+        <v>1904537.13</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>29712.35</v>
+        <v>29480.58</v>
       </c>
     </row>
   </sheetData>

--- a/asx_eod_output/Report_XLSX/Report_20260819.xlsx
+++ b/asx_eod_output/Report_XLSX/Report_20260819.xlsx
@@ -488,24 +488,24 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1.597</v>
+        <v>1.595</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.012</v>
+        <v>0.01</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>0.63%</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
         <v>153181</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>244630.06</v>
+        <v>244323.7</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>1838.17</v>
+        <v>1531.81</v>
       </c>
     </row>
     <row r="5">
@@ -542,24 +542,24 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1.17</v>
+        <v>1.175</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>-0.045</v>
+        <v>-0.04</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-3.70%</t>
+          <t>-3.29%</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
         <v>57458</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>67225.86</v>
+        <v>67513.14999999999</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-2585.61</v>
+        <v>-2298.32</v>
       </c>
     </row>
     <row r="7">
@@ -569,24 +569,24 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>63.58</v>
+        <v>63.57</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>-0.27</v>
+        <v>-0.28</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>-0.44%</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
         <v>11065</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>703512.7</v>
+        <v>703402.05</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-2987.55</v>
+        <v>-3098.2</v>
       </c>
     </row>
     <row r="8">
@@ -623,14 +623,14 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>160.17</v>
+        <v>160.27</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>-2.46</v>
+        <v>-2.36</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-1.51%</t>
+          <t>-1.45%</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
@@ -677,24 +677,24 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>165.8</v>
+        <v>165.88</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>7.98</v>
+        <v>8.06</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5.06%</t>
+          <t>5.11%</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
         <v>4000</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>663200</v>
+        <v>663520</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>31920</v>
+        <v>32240</v>
       </c>
     </row>
     <row r="12">
@@ -704,24 +704,24 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>0.275</v>
+        <v>0.265</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3.77%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
         <v>20000</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>5500</v>
+        <v>5300</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -812,14 +812,14 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>34.51</v>
+        <v>34.52</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>-0.40%</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
@@ -839,24 +839,24 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>33.6</v>
+        <v>33.58</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.33%</t>
+          <t>1.27%</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
         <v>1288</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>43276.8</v>
+        <v>43251.04</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>566.72</v>
+        <v>540.96</v>
       </c>
     </row>
     <row r="18">
@@ -870,10 +870,10 @@
       <c r="D18" s="5" t="inlineStr"/>
       <c r="E18" s="7" t="inlineStr"/>
       <c r="F18" s="8" t="n">
-        <v>1904537.13</v>
+        <v>1904501.65</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>29480.58</v>
+        <v>29445.1</v>
       </c>
     </row>
   </sheetData>

--- a/asx_eod_output/Report_XLSX/Report_20260819.xlsx
+++ b/asx_eod_output/Report_XLSX/Report_20260819.xlsx
@@ -542,24 +542,24 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1.175</v>
+        <v>1.17</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>-0.04</v>
+        <v>-0.045</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-3.29%</t>
+          <t>-3.70%</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
         <v>57458</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>67513.14999999999</v>
+        <v>67225.86</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-2298.32</v>
+        <v>-2585.61</v>
       </c>
     </row>
     <row r="7">
@@ -569,24 +569,24 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>63.57</v>
+        <v>63.71</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>-0.28</v>
+        <v>-0.14</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-0.44%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
         <v>11065</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>703402.05</v>
+        <v>704951.15</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-3098.2</v>
+        <v>-1549.1</v>
       </c>
     </row>
     <row r="8">
@@ -623,14 +623,14 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>160.27</v>
+        <v>160.71</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>-2.36</v>
+        <v>-1.92</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-1.45%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
@@ -677,24 +677,24 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>165.88</v>
+        <v>166.48</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>8.06</v>
+        <v>8.66</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5.11%</t>
+          <t>5.49%</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
         <v>4000</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>663520</v>
+        <v>665920</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>32240</v>
+        <v>34640</v>
       </c>
     </row>
     <row r="12">
@@ -812,14 +812,14 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>34.52</v>
+        <v>34.44</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.22</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-0.40%</t>
+          <t>-0.63%</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
@@ -839,24 +839,24 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>33.58</v>
+        <v>33.55</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>1.18%</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
         <v>1288</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>43251.04</v>
+        <v>43212.4</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>540.96</v>
+        <v>502.32</v>
       </c>
     </row>
     <row r="18">
@@ -870,10 +870,10 @@
       <c r="D18" s="5" t="inlineStr"/>
       <c r="E18" s="7" t="inlineStr"/>
       <c r="F18" s="8" t="n">
-        <v>1904501.65</v>
+        <v>1908124.81</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>29445.1</v>
+        <v>33068.27</v>
       </c>
     </row>
   </sheetData>
